--- a/Documentos/Documentos Excel - Hojas de calculo/Funciones de búsqueda y referencia.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Funciones de búsqueda y referencia.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="14">
   <si>
     <t>Código</t>
   </si>
@@ -202,7 +202,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F585F4-753E-058A-3963-104073AE5EE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{42F585F4-753E-058A-3963-104073AE5EE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -356,7 +356,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED03C79E-55AE-2FDF-A83E-B926E6EECB7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED03C79E-55AE-2FDF-A83E-B926E6EECB7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -553,7 +553,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6235F0BE-5366-8C8C-5C9E-1C225894339E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6235F0BE-5366-8C8C-5C9E-1C225894339E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -807,7 +807,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33FE2C19-583D-A577-6C34-364B423F2774}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{33FE2C19-583D-A577-6C34-364B423F2774}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1917,7 +1917,7 @@
   <cols>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1989,6 +1989,12 @@
       <c r="D4" s="3">
         <v>28710</v>
       </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
@@ -2004,6 +2010,10 @@
       <c r="D5" s="3">
         <v>24919</v>
       </c>
+      <c r="F5" s="3">
+        <v>36937</v>
+      </c>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">

--- a/Documentos/Documentos Excel - Hojas de calculo/Funciones de búsqueda y referencia.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Funciones de búsqueda y referencia.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="14">
   <si>
     <t>Código</t>
   </si>
@@ -194,15 +194,15 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{42F585F4-753E-058A-3963-104073AE5EE5}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F585F4-753E-058A-3963-104073AE5EE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -211,7 +211,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4772025" y="742950"/>
-          <a:ext cx="6581775" cy="1638300"/>
+          <a:ext cx="6581775" cy="2152650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -246,9 +246,27 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-AR" sz="1100"/>
+            <a:rPr lang="es-AR" sz="1100" b="1"/>
             <a:t>BUSCAR</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-AR" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Busca un valor en un rango y devuelve un resultado relacionado en otra posición.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-AR" sz="1100"/>
         </a:p>
         <a:p>
           <a:r>
@@ -356,7 +374,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED03C79E-55AE-2FDF-A83E-B926E6EECB7B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED03C79E-55AE-2FDF-A83E-B926E6EECB7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -400,9 +418,26 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-AR" sz="1100"/>
+            <a:rPr lang="es-AR" sz="1100" b="1"/>
             <a:t>BUSCARV</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-AR" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Busca un valor en la primera columna de una tabla y devuelve un dato de la misma fila.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-AR" sz="1100" b="1"/>
         </a:p>
         <a:p>
           <a:r>
@@ -545,15 +580,15 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6235F0BE-5366-8C8C-5C9E-1C225894339E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6235F0BE-5366-8C8C-5C9E-1C225894339E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -562,7 +597,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="219075" y="1962150"/>
-          <a:ext cx="4810125" cy="2019300"/>
+          <a:ext cx="4810125" cy="2533650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -597,7 +632,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-AR" sz="1100">
+            <a:rPr lang="es-AR" sz="1100" b="1">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -608,7 +643,32 @@
             </a:rPr>
             <a:t>BUSCARH</a:t>
           </a:r>
-          <a:endParaRPr lang="es-AR">
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-AR" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Busca un valor en la primera fila de una tabla y devuelve un dato de la misma columna.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-AR" sz="1100" b="1">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="es-AR" b="1">
             <a:effectLst/>
           </a:endParaRPr>
         </a:p>
@@ -799,15 +859,15 @@
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>85726</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{33FE2C19-583D-A577-6C34-364B423F2774}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33FE2C19-583D-A577-6C34-364B423F2774}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -816,7 +876,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="219074" y="2533650"/>
-          <a:ext cx="6229351" cy="1552576"/>
+          <a:ext cx="6324601" cy="2190750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -851,7 +911,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="es-AR" sz="1100">
+            <a:rPr lang="es-AR" sz="1100" b="1">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -862,6 +922,31 @@
             </a:rPr>
             <a:t>BUSCARX</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-AR" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Busca un valor en una columna o fila y devuelve el dato correspondiente desde otro rango. Puede buscar de arriba hacia abajo (en columnas) o de izquierda a derecha (en filas), lo que la hace más flexible que BUSCARV y BUSCARH.</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-AR" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="es-AR">
             <a:effectLst/>
           </a:endParaRPr>
@@ -2044,6 +2129,12 @@
       <c r="D7" s="3">
         <v>33852</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -2059,6 +2150,10 @@
       <c r="D8" s="3">
         <v>38332</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -2089,6 +2184,12 @@
       <c r="D10" s="3">
         <v>32154</v>
       </c>
+      <c r="F10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -2104,6 +2205,10 @@
       <c r="D11" s="3">
         <v>26575</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Documentos/Documentos Excel - Hojas de calculo/Funciones de búsqueda y referencia.xlsx
+++ b/Documentos/Documentos Excel - Hojas de calculo/Funciones de búsqueda y referencia.xlsx
@@ -202,7 +202,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42F585F4-753E-058A-3963-104073AE5EE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{42F585F4-753E-058A-3963-104073AE5EE5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -374,7 +374,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED03C79E-55AE-2FDF-A83E-B926E6EECB7B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED03C79E-55AE-2FDF-A83E-B926E6EECB7B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -588,7 +588,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6235F0BE-5366-8C8C-5C9E-1C225894339E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6235F0BE-5366-8C8C-5C9E-1C225894339E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -712,7 +712,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> BUSCADO; MATRIZ TABLA; INDICADOR DE COLUMNAS; RANGO)</a:t>
+            <a:t> BUSCADO; MATRIZ TABLA; INDICADOR DE FILAS; RANGO)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -867,7 +867,7 @@
         <xdr:cNvPr id="3" name="CuadroTexto 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33FE2C19-583D-A577-6C34-364B423F2774}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{33FE2C19-583D-A577-6C34-364B423F2774}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>36646</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>36646</v>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2">
         <f t="shared" ca="1" si="0"/>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="3">
         <v>36646</v>
